--- a/data/trans_dic/P17G_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,97</t>
+          <t>2,02; 6,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,98</t>
+          <t>2,38; 8,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,59</t>
+          <t>0,65; 5,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,46</t>
+          <t>0,9; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,41</t>
+          <t>0,6; 3,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,83</t>
+          <t>1,73; 4,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,96</t>
+          <t>1,96; 5,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,51</t>
+          <t>0,16; 1,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,12</t>
+          <t>1,89; 4,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,91</t>
+          <t>1,42; 3,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,66</t>
+          <t>0,2; 2,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,75</t>
+          <t>0,61; 3,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,52</t>
+          <t>0,21; 2,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,99</t>
+          <t>0,68; 3,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,48</t>
+          <t>1,05; 3,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,61</t>
+          <t>0,59; 2,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,76</t>
+          <t>0,42; 2,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,74</t>
+          <t>0,69; 2,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,52</t>
+          <t>0,81; 2,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,63</t>
+          <t>0,82; 2,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,11</t>
+          <t>0,52; 2,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,35</t>
+          <t>0,8; 2,37</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,9</t>
+          <t>0,3; 3,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,73</t>
+          <t>0,3; 2,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,96</t>
+          <t>0,81; 3,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,28</t>
+          <t>0,42; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,28</t>
+          <t>0,26; 2,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,75</t>
+          <t>0,29; 3,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,26</t>
+          <t>0,55; 3,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,37</t>
+          <t>1,02; 3,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,19</t>
+          <t>0,42; 1,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,65</t>
+          <t>0,58; 2,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,89</t>
+          <t>0,87; 2,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,73</t>
+          <t>0,98; 2,65</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,03</t>
+          <t>0,25; 2,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,65</t>
+          <t>0,58; 4,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,89</t>
+          <t>0,26; 2,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,15</t>
+          <t>0,97; 4,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,66</t>
+          <t>0,46; 2,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,02</t>
+          <t>0,24; 2,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,9</t>
+          <t>1,75; 5,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,24</t>
+          <t>0,79; 3,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,98</t>
+          <t>0,48; 1,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,66</t>
+          <t>0,64; 2,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,68</t>
+          <t>1,19; 3,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,17</t>
+          <t>1,19; 3,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,98</t>
+          <t>0,48; 4,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,78</t>
+          <t>0,45; 4,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,2</t>
+          <t>0,5; 5,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,15</t>
+          <t>0,94; 5,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,76</t>
+          <t>0,59; 3,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,25</t>
+          <t>0,67; 3,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,91</t>
+          <t>1,14; 3,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,19</t>
+          <t>0,46; 3,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,45</t>
+          <t>0,58; 2,59</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,44</t>
+          <t>0,36; 3,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,58</t>
+          <t>0,36; 3,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,41</t>
+          <t>0,64; 3,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,73</t>
+          <t>0,33; 1,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,34</t>
+          <t>0,53; 2,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,92</t>
+          <t>0,48; 1,96</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,34</t>
+          <t>0,62; 2,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,04</t>
+          <t>0,97; 3,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,82</t>
+          <t>0,51; 2,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,76</t>
+          <t>2,0; 5,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,08</t>
+          <t>0,78; 2,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,73</t>
+          <t>1,17; 3,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,52</t>
+          <t>0,67; 2,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,57</t>
+          <t>1,61; 5,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,35</t>
+          <t>0,86; 2,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,97</t>
+          <t>1,31; 2,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,21</t>
+          <t>0,77; 2,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,84</t>
+          <t>2,21; 5,04</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,77</t>
+          <t>0,83; 2,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,18</t>
+          <t>0,51; 2,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,57</t>
+          <t>1,5; 3,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,94</t>
+          <t>0,34; 2,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,14</t>
+          <t>1,11; 3,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,59</t>
+          <t>0,26; 1,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,34</t>
+          <t>1,53; 4,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,28</t>
+          <t>0,86; 2,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,61</t>
+          <t>1,16; 2,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,63</t>
+          <t>0,51; 1,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,4</t>
+          <t>1,8; 3,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,81</t>
+          <t>0,67; 1,86</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,88</t>
+          <t>1,03; 1,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1847,52 +1847,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,36</t>
+          <t>1,37; 2,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,33</t>
+          <t>1,26; 2,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,12</t>
+          <t>1,27; 2,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,66</t>
+          <t>0,9; 1,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,47</t>
+          <t>1,4; 2,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,62</t>
+          <t>1,68; 2,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,84</t>
+          <t>1,23; 1,85</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,61</t>
+          <t>1,02; 1,6</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,23</t>
+          <t>1,52; 2,18</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,31</t>
+          <t>1,62; 2,35</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5522; 19017</t>
+          <t>5501; 18172</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6172</t>
+          <t>0; 5106</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6759; 23429</t>
+          <t>6987; 23528</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1836; 14297</t>
+          <t>2011; 15754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3080; 14237</t>
+          <t>2352; 14078</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7052</t>
+          <t>0; 6969</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1688; 9833</t>
+          <t>1722; 10612</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4839; 13935</t>
+          <t>5003; 13925</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10579; 26484</t>
+          <t>10474; 27621</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>954; 8795</t>
+          <t>952; 8933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10638; 29831</t>
+          <t>11025; 28672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8267; 23465</t>
+          <t>8510; 23541</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>997; 13126</t>
+          <t>989; 12786</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3020; 18673</t>
+          <t>3039; 17724</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1098; 12659</t>
+          <t>1039; 12893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3467; 15454</t>
+          <t>3499; 16231</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5016; 17528</t>
+          <t>5282; 17380</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3076; 13637</t>
+          <t>3076; 14436</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2188; 14366</t>
+          <t>2177; 12806</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3505; 14100</t>
+          <t>3563; 12732</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8780; 25108</t>
+          <t>8083; 25960</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8944; 26813</t>
+          <t>8417; 27262</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6041; 21576</t>
+          <t>5286; 21694</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8871; 24257</t>
+          <t>8276; 24498</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>942; 9249</t>
+          <t>952; 11161</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>933; 8688</t>
+          <t>947; 8689</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2716; 12550</t>
+          <t>2578; 12243</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1626; 10366</t>
+          <t>1330; 10212</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>883; 7585</t>
+          <t>881; 7492</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>987; 12646</t>
+          <t>965; 11890</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1941; 10918</t>
+          <t>1827; 10438</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3499; 11771</t>
+          <t>3564; 12633</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2541; 14303</t>
+          <t>2712; 12970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3704; 17356</t>
+          <t>3777; 17846</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6399; 18812</t>
+          <t>5689; 19253</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6077; 18145</t>
+          <t>6549; 17612</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>898; 7278</t>
+          <t>895; 7412</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2987; 17307</t>
+          <t>2176; 16088</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>965; 10644</t>
+          <t>968; 10849</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3157; 16098</t>
+          <t>3017; 14326</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1796; 9885</t>
+          <t>1697; 9801</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>904; 7620</t>
+          <t>903; 7651</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6685; 22705</t>
+          <t>6749; 22420</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3513; 15391</t>
+          <t>3743; 15377</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3722; 14423</t>
+          <t>3500; 13861</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4848; 19942</t>
+          <t>4832; 20379</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9364; 27719</t>
+          <t>8993; 28230</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9095; 25014</t>
+          <t>9371; 25397</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5213</t>
+          <t>0; 5380</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1016; 8411</t>
+          <t>1005; 9200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>945; 10039</t>
+          <t>936; 9847</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4932</t>
+          <t>0; 4911</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1036; 10795</t>
+          <t>1030; 11636</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2038; 11309</t>
+          <t>2070; 12015</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7225</t>
+          <t>0; 6062</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1491; 7804</t>
+          <t>1216; 7974</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2648; 13350</t>
+          <t>2738; 14105</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4140; 16867</t>
+          <t>4911; 16872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1924; 13625</t>
+          <t>1947; 13428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2250; 9453</t>
+          <t>2250; 10020</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>946; 9309</t>
+          <t>973; 10124</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6174</t>
+          <t>0; 6936</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>448; 3863</t>
+          <t>446; 3860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4814</t>
+          <t>0; 4336</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>950; 9511</t>
+          <t>970; 9598</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1668; 8764</t>
+          <t>1640; 9002</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1733; 9509</t>
+          <t>1802; 10334</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2075; 12289</t>
+          <t>2781; 11925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2722; 10092</t>
+          <t>2533; 10330</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2956; 14291</t>
+          <t>3805; 14953</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5926; 20113</t>
+          <t>6404; 20358</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3813; 18530</t>
+          <t>3333; 16473</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12801; 35982</t>
+          <t>12456; 36360</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4830; 19649</t>
+          <t>4968; 18774</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8555; 25821</t>
+          <t>8069; 25222</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4398; 17418</t>
+          <t>4598; 17385</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14348; 47210</t>
+          <t>13632; 47388</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10659; 29336</t>
+          <t>10714; 27772</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17584; 40124</t>
+          <t>17724; 38588</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10666; 29753</t>
+          <t>10429; 28607</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>31173; 71245</t>
+          <t>32607; 74278</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6032; 20582</t>
+          <t>6153; 21326</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3152; 16881</t>
+          <t>3969; 18638</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12011; 27690</t>
+          <t>11603; 29948</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2947; 18003</t>
+          <t>3155; 19121</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7812; 24574</t>
+          <t>8687; 25174</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2096; 12994</t>
+          <t>2115; 13105</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13209; 35557</t>
+          <t>12564; 33843</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5496; 16361</t>
+          <t>6196; 16709</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17557; 39783</t>
+          <t>17743; 39172</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8332; 25886</t>
+          <t>8160; 24971</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28285; 54197</t>
+          <t>28673; 54484</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10892; 29821</t>
+          <t>11091; 30663</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>33859; 61432</t>
+          <t>33614; 62190</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>31342; 60654</t>
+          <t>31422; 60509</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45609; 79830</t>
+          <t>46226; 76927</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42980; 80472</t>
+          <t>43574; 80559</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>41338; 71712</t>
+          <t>42750; 74119</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32042; 58504</t>
+          <t>31770; 61314</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51758; 86960</t>
+          <t>49277; 84521</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>61378; 95841</t>
+          <t>61488; 97143</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>83093; 122514</t>
+          <t>81811; 123182</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>70533; 111291</t>
+          <t>70865; 110733</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>104946; 153876</t>
+          <t>105130; 150567</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>112788; 164489</t>
+          <t>115007; 167168</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,66</t>
+          <t>1,88; 6,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,01</t>
+          <t>2,49; 8,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,06</t>
+          <t>0,69; 4,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,4</t>
+          <t>1,01; 5,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,68</t>
+          <t>0,57; 3,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,82</t>
+          <t>1,48; 4,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,17</t>
+          <t>2,05; 5,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,54</t>
+          <t>0,16; 1,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,92</t>
+          <t>1,87; 5,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,92</t>
+          <t>1,43; 3,58</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,59</t>
+          <t>0,2; 2,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,55</t>
+          <t>0,6; 3,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,57</t>
+          <t>0,21; 2,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,14</t>
+          <t>0,67; 3,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,45</t>
+          <t>1,02; 3,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,46</t>
+          <t>0,42; 2,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,47</t>
+          <t>0,63; 2,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,6</t>
+          <t>0,85; 2,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,67</t>
+          <t>0,82; 2,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,12</t>
+          <t>0,52; 2,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,37</t>
+          <t>0,85; 2,37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,5</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,73</t>
+          <t>0,29; 2,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,87</t>
+          <t>0,85; 3,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,23</t>
+          <t>0,39; 3,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,53</t>
+          <t>0,29; 4,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,12</t>
+          <t>0,55; 3,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,62</t>
+          <t>0,94; 3,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,99</t>
+          <t>0,3; 2,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,73</t>
+          <t>0,57; 2,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,96</t>
+          <t>0,88; 2,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,65</t>
+          <t>0,94; 2,67</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,07</t>
+          <t>0,25; 2,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,32</t>
+          <t>0,8; 4,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,95</t>
+          <t>0,26; 2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,58</t>
+          <t>0,88; 4,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,64</t>
+          <t>0,48; 2,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,03</t>
+          <t>0,24; 2,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,82</t>
+          <t>1,79; 6,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,24</t>
+          <t>1,01; 3,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,9</t>
+          <t>0,39; 1,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,72</t>
+          <t>0,7; 2,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,75</t>
+          <t>1,25; 3,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,22</t>
+          <t>1,2; 3,42</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,35</t>
+          <t>0,48; 4,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,69</t>
+          <t>0,45; 4,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,6</t>
+          <t>0,5; 5,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,47</t>
+          <t>0,94; 5,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,84</t>
+          <t>0,72; 3,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,43</t>
+          <t>0,68; 3,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,91</t>
+          <t>1,1; 3,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,14</t>
+          <t>0,46; 3,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,59</t>
+          <t>0,57; 2,44</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,74</t>
+          <t>0,36; 3,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,43</t>
+          <t>0,17; 1,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,61</t>
+          <t>0,36; 3,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,5</t>
+          <t>0,62; 3,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,27</t>
+          <t>0,39; 2,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,96</t>
+          <t>0,53; 1,99</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,45</t>
+          <t>0,62; 2,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,08</t>
+          <t>0,9; 2,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,51</t>
+          <t>0,54; 2,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,82</t>
+          <t>1,99; 5,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,94</t>
+          <t>0,73; 2,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,65</t>
+          <t>1,27; 3,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,52</t>
+          <t>0,73; 2,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,59</t>
+          <t>3,35; 6,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,22</t>
+          <t>0,87; 2,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,85</t>
+          <t>1,31; 2,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,12</t>
+          <t>0,8; 2,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,04</t>
+          <t>3,15; 5,36</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,87</t>
+          <t>0,88; 2,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,41</t>
+          <t>0,42; 2,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,86</t>
+          <t>1,47; 3,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,06</t>
+          <t>0,59; 2,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,21</t>
+          <t>1,01; 3,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,6</t>
+          <t>0,25; 1,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,13</t>
+          <t>1,62; 4,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,33</t>
+          <t>0,79; 2,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,57</t>
+          <t>1,16; 2,59</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,57</t>
+          <t>0,5; 1,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,42</t>
+          <t>1,78; 3,5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,86</t>
+          <t>0,86; 2,0</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,9</t>
+          <t>1,05; 1,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,78</t>
+          <t>0,92; 1,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,27</t>
+          <t>1,39; 2,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,33</t>
+          <t>1,36; 2,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,19</t>
+          <t>1,22; 2,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,74</t>
+          <t>0,86; 1,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,4</t>
+          <t>1,43; 2,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,66</t>
+          <t>1,88; 2,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,85</t>
+          <t>1,26; 1,87</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,6</t>
+          <t>0,99; 1,55</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,18</t>
+          <t>1,54; 2,18</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,35</t>
+          <t>1,75; 2,41</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>14044</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5501; 18172</t>
+          <t>5128; 18150</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5106</t>
+          <t>0; 5415</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6987; 23528</t>
+          <t>7306; 23497</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2011; 15754</t>
+          <t>2213; 13070</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2352; 14078</t>
+          <t>2630; 13395</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6969</t>
+          <t>0; 7084</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1722; 10612</t>
+          <t>1644; 9878</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5003; 13925</t>
+          <t>4666; 13423</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10474; 27621</t>
+          <t>10961; 28146</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>952; 8933</t>
+          <t>942; 8092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11025; 28672</t>
+          <t>10890; 29422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8510; 23541</t>
+          <t>9052; 22672</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15634</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>989; 12786</t>
+          <t>991; 13365</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3039; 17724</t>
+          <t>2995; 17469</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1039; 12893</t>
+          <t>1060; 12073</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3499; 16231</t>
+          <t>3557; 15959</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5282; 17380</t>
+          <t>5158; 18895</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3076; 14436</t>
+          <t>3081; 14413</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2177; 12806</t>
+          <t>2190; 12657</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3563; 12732</t>
+          <t>3446; 13844</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8083; 25960</t>
+          <t>8493; 24552</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8417; 27262</t>
+          <t>8394; 26725</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5286; 21694</t>
+          <t>5314; 20737</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8276; 24498</t>
+          <t>9116; 25516</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>11202</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>952; 11161</t>
+          <t>0; 10709</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>947; 8689</t>
+          <t>935; 8601</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2578; 12243</t>
+          <t>2696; 12340</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1330; 10212</t>
+          <t>1247; 9665</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>881; 7492</t>
+          <t>883; 7509</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>965; 11890</t>
+          <t>983; 13481</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1827; 10438</t>
+          <t>1845; 11470</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3564; 12633</t>
+          <t>3348; 12156</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2712; 12970</t>
+          <t>1970; 13957</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3777; 17846</t>
+          <t>3742; 16275</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5689; 19253</t>
+          <t>5706; 18713</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6549; 17612</t>
+          <t>6330; 17978</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>16189</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>895; 7412</t>
+          <t>899; 8206</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2176; 16088</t>
+          <t>2990; 16712</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>968; 10849</t>
+          <t>952; 10466</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3017; 14326</t>
+          <t>3289; 17086</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1697; 9801</t>
+          <t>1792; 9524</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>903; 7651</t>
+          <t>904; 7563</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6749; 22420</t>
+          <t>6901; 24047</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3743; 15377</t>
+          <t>4254; 15666</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3500; 13861</t>
+          <t>2858; 13472</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4832; 20379</t>
+          <t>5216; 22082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8993; 28230</t>
+          <t>9384; 27158</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9371; 25397</t>
+          <t>9564; 27182</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5207</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5380</t>
+          <t>0; 5820</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1005; 9200</t>
+          <t>1008; 9259</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>936; 9847</t>
+          <t>937; 9815</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4911</t>
+          <t>0; 5412</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1030; 11636</t>
+          <t>1033; 12283</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2070; 12015</t>
+          <t>2055; 12997</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6062</t>
+          <t>0; 6797</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1216; 7974</t>
+          <t>1625; 8757</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2738; 14105</t>
+          <t>2796; 14339</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4911; 16872</t>
+          <t>4736; 16862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1947; 13428</t>
+          <t>1953; 14412</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2250; 10020</t>
+          <t>2461; 10528</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5321</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>973; 10124</t>
+          <t>965; 9360</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3259,17 +3259,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6936</t>
+          <t>0; 7173</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>446; 3860</t>
+          <t>449; 4232</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4336</t>
+          <t>0; 4714</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,17 +3279,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>970; 9598</t>
+          <t>958; 10248</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1640; 9002</t>
+          <t>1641; 8319</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1802; 10334</t>
+          <t>1839; 10310</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2781; 11925</t>
+          <t>2045; 13429</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2533; 10330</t>
+          <t>2857; 10632</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>31195</t>
+          <t>35377</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>52839</t>
+          <t>60017</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3805; 14953</t>
+          <t>3801; 15187</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6404; 20358</t>
+          <t>5953; 19584</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3333; 16473</t>
+          <t>3565; 17679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12456; 36360</t>
+          <t>14309; 39208</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4968; 18774</t>
+          <t>4643; 19000</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8069; 25222</t>
+          <t>8796; 25641</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4598; 17385</t>
+          <t>5005; 17639</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13632; 47388</t>
+          <t>25855; 47710</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10714; 27772</t>
+          <t>10879; 29420</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17724; 38588</t>
+          <t>17701; 40266</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10429; 28607</t>
+          <t>10775; 28265</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32607; 74278</t>
+          <t>46893; 79927</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>21756</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6153; 21326</t>
+          <t>6507; 20778</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3969; 18638</t>
+          <t>3268; 16928</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11603; 29948</t>
+          <t>11426; 29790</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3155; 19121</t>
+          <t>4675; 19407</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8687; 25174</t>
+          <t>7913; 25099</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2115; 13105</t>
+          <t>2069; 12648</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12564; 33843</t>
+          <t>13280; 34145</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6196; 16709</t>
+          <t>6583; 19240</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17743; 39172</t>
+          <t>17690; 39608</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8160; 24971</t>
+          <t>8040; 24970</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28673; 54484</t>
+          <t>28318; 55846</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11091; 30663</t>
+          <t>13956; 32570</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>79255</t>
+          <t>85324</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>138661</t>
+          <t>149368</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>33614; 62190</t>
+          <t>34362; 63320</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>31422; 60509</t>
+          <t>31284; 61554</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46226; 76927</t>
+          <t>46905; 80693</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43574; 80559</t>
+          <t>47851; 85395</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>42750; 74119</t>
+          <t>41285; 70942</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31770; 61314</t>
+          <t>30292; 57277</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49277; 84521</t>
+          <t>50316; 83512</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>61488; 97143</t>
+          <t>69989; 104437</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>81811; 123182</t>
+          <t>83428; 124147</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>70865; 110733</t>
+          <t>68540; 107747</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>105130; 150567</t>
+          <t>106017; 150857</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>115007; 167168</t>
+          <t>127400; 174814</t>
         </is>
       </c>
     </row>
